--- a/performance-dashboard/reports/daily/交易表现分析.xlsx
+++ b/performance-dashboard/reports/daily/交易表现分析.xlsx
@@ -531,26 +531,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,019,638.10</t>
+          <t>¥1,024,948.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+19,638.10</t>
+          <t>¥+24,948.95</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.96%</t>
+          <t>+2.49%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+35.84%</t>
+          <t>+44.09%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4.648</v>
+        <v>5.605</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -559,24 +559,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1306%</t>
+          <t>0.1550%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6.6552%</t>
+          <t>6.6161%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -607,26 +607,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,042,439.98</t>
+          <t>¥1,049,943.89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+42,439.98</t>
+          <t>¥+49,943.89</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+4.24%</t>
+          <t>+4.99%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+92.44%</t>
+          <t>+105.95%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6.638</v>
+        <v>7.444</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,24 +635,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.2796%</t>
+          <t>0.3071%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10.3159%</t>
+          <t>10.1306%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -683,26 +683,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,014,809.18</t>
+          <t>¥1,020,348.80</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+14,809.18</t>
+          <t>¥+20,348.80</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.48%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+26.05%</t>
+          <t>+34.80%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4.431</v>
+        <v>5.661</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -711,24 +711,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0986%</t>
+          <t>0.1265%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5.1597%</t>
+          <t>5.2833%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -759,26 +759,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,003,464.49</t>
+          <t>¥1,004,906.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+3,464.49</t>
+          <t>¥+4,906.39</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+5.60%</t>
+          <t>+7.52%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.575</v>
+        <v>2.382</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -787,24 +787,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0232%</t>
+          <t>0.0307%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.4506%</t>
+          <t>2.4176%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -835,26 +835,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,001,518.00</t>
+          <t>¥1,004,115.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+1,518.00</t>
+          <t>¥+4,115.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.42%</t>
+          <t>+6.28%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.472</v>
+        <v>2.96</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -863,24 +863,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0101%</t>
+          <t>0.0257%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.2193%</t>
+          <t>1.5200%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -911,26 +911,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>¥1,040,563.19</t>
+          <t>¥1,045,139.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>¥+40,563.19</t>
+          <t>¥+45,139.78</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+4.06%</t>
+          <t>+4.51%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+87.06%</t>
+          <t>+92.41%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>8.300000000000001</v>
+        <v>8.896000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -939,24 +939,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.2667%</t>
+          <t>0.2775%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>7.8577%</t>
+          <t>7.6372%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -987,26 +987,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>¥1,026,881.61</t>
+          <t>¥1,032,294.79</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>¥+26,881.61</t>
+          <t>¥+32,294.79</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.69%</t>
+          <t>+3.23%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+51.86%</t>
+          <t>+60.18%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6.192</v>
+        <v>7.075</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1015,24 +1015,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.1779%</t>
+          <t>0.1998%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6.9223%</t>
+          <t>6.8355%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1063,26 +1063,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>¥1,030,262.17</t>
+          <t>¥1,035,821.52</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>¥+30,262.17</t>
+          <t>¥+35,821.52</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>+3.58%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+59.93%</t>
+          <t>+68.49%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.98</v>
+        <v>7.859</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1091,24 +1091,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.1999%</t>
+          <t>0.2211%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6.9331%</t>
+          <t>6.8387%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1139,26 +1139,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>¥1,052,440.53</t>
+          <t>¥1,059,434.88</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>¥+52,440.53</t>
+          <t>¥+59,434.88</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+5.24%</t>
+          <t>+5.94%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+123.67%</t>
+          <t>+135.34%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.436</v>
+        <v>8.087</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1167,24 +1167,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.3439%</t>
+          <t>0.3639%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>11.3886%</t>
+          <t>11.0956%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1215,26 +1215,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>¥1,002,594.00</t>
+          <t>¥1,004,915.00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>¥+2,594.00</t>
+          <t>¥+4,915.00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+4.16%</t>
+          <t>+7.54%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2.387</v>
+        <v>4.536</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1243,24 +1243,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.0173%</t>
+          <t>0.0307%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.9959%</t>
+          <t>1.2678%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1291,26 +1291,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>¥1,011,144.42</t>
+          <t>¥1,014,230.30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>¥+11,144.42</t>
+          <t>¥+14,230.30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>+1.42%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+19.07%</t>
+          <t>+23.30%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3.44</v>
+        <v>4.249</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1319,24 +1319,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.0744%</t>
+          <t>0.0888%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4.8735%</t>
+          <t>4.8014%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1367,26 +1367,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>¥1,042,601.48</t>
+          <t>¥1,049,086.38</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>¥+42,601.48</t>
+          <t>¥+49,086.38</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+4.26%</t>
+          <t>+4.91%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+92.91%</t>
+          <t>+103.47%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.292</v>
+        <v>6.952</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1395,24 +1395,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.2809%</t>
+          <t>0.3022%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>10.9356%</t>
+          <t>10.6692%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1443,26 +1443,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>¥1,007,811.62</t>
+          <t>¥1,011,061.62</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>¥+7,811.62</t>
+          <t>¥+11,061.62</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+13.04%</t>
+          <t>+17.71%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3.849</v>
+        <v>5.152</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1471,24 +1471,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.0521%</t>
+          <t>0.0690%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2.8938%</t>
+          <t>2.9884%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1519,26 +1519,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>¥1,000,596.60</t>
+          <t>¥1,001,327.00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>¥+596.60</t>
+          <t>¥+1,327.00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-2.063</v>
+        <v>0.207</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1547,24 +1547,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.0040%</t>
+          <t>0.0083%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.4737%</t>
+          <t>0.5298%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1595,26 +1595,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>¥1,000,663.50</t>
+          <t>¥1,001,421.90</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>¥+663.50</t>
+          <t>¥+1,421.90</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>+2.13%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-1.82</v>
+        <v>0.484</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1623,24 +1623,24 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.0044%</t>
+          <t>0.0089%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.4752%</t>
+          <t>0.5356%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1767,26 +1767,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,019,638.10</t>
+          <t>¥1,024,948.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+19,638.10</t>
+          <t>¥+24,948.95</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.96%</t>
+          <t>+2.49%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+35.84%</t>
+          <t>+44.09%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4.648</v>
+        <v>5.605</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1795,24 +1795,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1306%</t>
+          <t>0.1550%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6.6552%</t>
+          <t>6.6161%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1843,26 +1843,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,042,439.98</t>
+          <t>¥1,049,943.89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+42,439.98</t>
+          <t>¥+49,943.89</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+4.24%</t>
+          <t>+4.99%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+92.44%</t>
+          <t>+105.95%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6.638</v>
+        <v>7.444</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1871,24 +1871,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.2796%</t>
+          <t>0.3071%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10.3159%</t>
+          <t>10.1306%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1919,26 +1919,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,014,809.18</t>
+          <t>¥1,020,348.80</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+14,809.18</t>
+          <t>¥+20,348.80</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.48%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+26.05%</t>
+          <t>+34.80%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4.431</v>
+        <v>5.661</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1947,24 +1947,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0986%</t>
+          <t>0.1265%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5.1597%</t>
+          <t>5.2833%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -1995,26 +1995,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,003,464.49</t>
+          <t>¥1,004,906.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+3,464.49</t>
+          <t>¥+4,906.39</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+5.60%</t>
+          <t>+7.52%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.575</v>
+        <v>2.382</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2023,24 +2023,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0232%</t>
+          <t>0.0307%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.4506%</t>
+          <t>2.4176%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2071,26 +2071,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,001,518.00</t>
+          <t>¥1,004,115.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+1,518.00</t>
+          <t>¥+4,115.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.42%</t>
+          <t>+6.28%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.472</v>
+        <v>2.96</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2099,24 +2099,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0101%</t>
+          <t>0.0257%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.2193%</t>
+          <t>1.5200%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2243,26 +2243,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,040,563.19</t>
+          <t>¥1,045,139.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+40,563.19</t>
+          <t>¥+45,139.78</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+4.06%</t>
+          <t>+4.51%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+87.06%</t>
+          <t>+92.41%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.896000000000001</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2271,24 +2271,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.2667%</t>
+          <t>0.2775%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7.8577%</t>
+          <t>7.6372%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2319,26 +2319,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,026,881.61</t>
+          <t>¥1,032,294.79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+26,881.61</t>
+          <t>¥+32,294.79</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+2.69%</t>
+          <t>+3.23%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+51.86%</t>
+          <t>+60.18%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6.192</v>
+        <v>7.075</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2347,24 +2347,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1779%</t>
+          <t>0.1998%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6.9223%</t>
+          <t>6.8355%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2395,26 +2395,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,030,262.17</t>
+          <t>¥1,035,821.52</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+30,262.17</t>
+          <t>¥+35,821.52</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>+3.58%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+59.93%</t>
+          <t>+68.49%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6.98</v>
+        <v>7.859</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2423,24 +2423,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.1999%</t>
+          <t>0.2211%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>6.9331%</t>
+          <t>6.8387%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2471,26 +2471,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,052,440.53</t>
+          <t>¥1,059,434.88</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+52,440.53</t>
+          <t>¥+59,434.88</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+5.24%</t>
+          <t>+5.94%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+123.67%</t>
+          <t>+135.34%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7.436</v>
+        <v>8.087</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2499,24 +2499,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.3439%</t>
+          <t>0.3639%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>11.3886%</t>
+          <t>11.0956%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2547,26 +2547,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,002,594.00</t>
+          <t>¥1,004,915.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+2,594.00</t>
+          <t>¥+4,915.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+4.16%</t>
+          <t>+7.54%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.387</v>
+        <v>4.536</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2575,24 +2575,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0173%</t>
+          <t>0.0307%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.9959%</t>
+          <t>1.2678%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2719,26 +2719,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,011,144.42</t>
+          <t>¥1,014,230.30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+11,144.42</t>
+          <t>¥+14,230.30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>+1.42%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+19.07%</t>
+          <t>+23.30%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.44</v>
+        <v>4.249</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2747,24 +2747,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0744%</t>
+          <t>0.0888%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4.8735%</t>
+          <t>4.8014%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2795,26 +2795,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,042,601.48</t>
+          <t>¥1,049,086.38</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+42,601.48</t>
+          <t>¥+49,086.38</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+4.26%</t>
+          <t>+4.91%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+92.91%</t>
+          <t>+103.47%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6.292</v>
+        <v>6.952</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2823,24 +2823,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.2809%</t>
+          <t>0.3022%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10.9356%</t>
+          <t>10.6692%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2871,26 +2871,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,007,811.62</t>
+          <t>¥1,011,061.62</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+7,811.62</t>
+          <t>¥+11,061.62</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+13.04%</t>
+          <t>+17.71%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3.849</v>
+        <v>5.152</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2899,24 +2899,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0521%</t>
+          <t>0.0690%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.8938%</t>
+          <t>2.9884%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -2947,26 +2947,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,000,596.60</t>
+          <t>¥1,001,327.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+596.60</t>
+          <t>¥+1,327.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-2.063</v>
+        <v>0.207</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2975,24 +2975,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0040%</t>
+          <t>0.0083%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.4737%</t>
+          <t>0.5298%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>
@@ -3023,26 +3023,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,000,663.50</t>
+          <t>¥1,001,421.90</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+663.50</t>
+          <t>¥+1,421.90</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>+2.13%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-1.82</v>
+        <v>0.484</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3051,24 +3051,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0044%</t>
+          <t>0.0089%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.4752%</t>
+          <t>0.5356%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260109</t>
+          <t>20260112</t>
         </is>
       </c>
     </row>

--- a/performance-dashboard/reports/daily/交易表现分析.xlsx
+++ b/performance-dashboard/reports/daily/交易表现分析.xlsx
@@ -531,26 +531,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,010,554.01</t>
+          <t>¥1,032,327.15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+10,554.01</t>
+          <t>¥+32,327.15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>+3.23%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+8.62%</t>
+          <t>+27.50%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.438</v>
+        <v>1.264</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -559,24 +559,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0414%</t>
+          <t>0.1074%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19.2732%</t>
+          <t>19.8473%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -683,26 +683,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥999,897.23</t>
+          <t>¥1,013,995.87</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥-102.77</t>
+          <t>¥+13,995.87</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.40%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+11.20%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-0.076</v>
+        <v>0.697</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -711,24 +711,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0036%</t>
+          <t>0.0476%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14.0505%</t>
+          <t>14.3644%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -835,26 +835,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,003,463.46</t>
+          <t>¥1,015,237.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+3,463.46</t>
+          <t>¥+15,237.23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.76%</t>
+          <t>+12.24%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.133</v>
+        <v>1.007</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -863,24 +863,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0132%</t>
+          <t>0.0494%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10.0520%</t>
+          <t>10.3997%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -911,26 +911,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>¥1,044,845.94</t>
+          <t>¥1,050,309.94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>¥+44,845.94</t>
+          <t>¥+50,309.94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+4.48%</t>
+          <t>+5.03%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+41.27%</t>
+          <t>+45.47%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3.967</v>
+        <v>4.351</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -939,24 +939,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.1431%</t>
+          <t>0.1550%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8.5895%</t>
+          <t>8.5191%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -987,26 +987,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>¥1,020,044.35</t>
+          <t>¥1,030,867.82</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>¥+20,044.35</t>
+          <t>¥+30,867.82</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.00%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+16.92%</t>
+          <t>+26.13%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.805</v>
+        <v>2.67</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1015,24 +1015,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.0653%</t>
+          <t>0.0964%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8.0199%</t>
+          <t>8.3590%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1063,26 +1063,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>¥1,004,929.36</t>
+          <t>¥1,023,654.23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>¥+4,929.36</t>
+          <t>¥+23,654.23</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+2.37%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+3.95%</t>
+          <t>+19.55%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.206</v>
+        <v>1.051</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1091,24 +1091,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.0214%</t>
+          <t>0.0789%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>16.5132%</t>
+          <t>17.0308%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1215,26 +1215,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>¥1,002,361.69</t>
+          <t>¥1,014,715.29</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>¥+2,361.69</t>
+          <t>¥+14,715.29</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.87%</t>
+          <t>+11.80%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.049</v>
+        <v>0.91</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1243,24 +1243,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.0100%</t>
+          <t>0.0482%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10.8078%</t>
+          <t>11.1606%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1291,26 +1291,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>¥992,161.83</t>
+          <t>¥1,010,898.93</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>¥-7,838.17</t>
+          <t>¥+10,898.93</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.01%</t>
+          <t>+8.63%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-0.441</v>
+        <v>0.478</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1319,24 +1319,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-0.0202%</t>
+          <t>0.0395%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16.0361%</t>
+          <t>16.6408%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1367,26 +1367,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>¥995,189.39</t>
+          <t>¥997,512.81</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>¥-4,810.61</t>
+          <t>¥-2,487.19</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.97%</t>
+          <t>-2.00%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-0.191</v>
+        <v>-0.095</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1395,24 +1395,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-0.0079%</t>
+          <t>0.0002%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>20.7391%</t>
+          <t>20.4021%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1443,26 +1443,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>¥1,001,757.22</t>
+          <t>¥1,012,531.22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>¥+1,757.22</t>
+          <t>¥+12,531.22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>+9.98%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>-0.005</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1471,24 +1471,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.0077%</t>
+          <t>0.0410%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>10.0141%</t>
+          <t>10.2882%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1519,26 +1519,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>¥996,835.60</t>
+          <t>¥1,000,956.00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>¥-3,164.40</t>
+          <t>¥+956.00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>+0.73%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-1.234</v>
+        <v>-0.307</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1547,24 +1547,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-0.0100%</t>
+          <t>0.0033%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>3.6381%</t>
+          <t>3.7668%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1595,26 +1595,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>¥997,466.80</t>
+          <t>¥1,002,799.30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>¥-2,533.20</t>
+          <t>¥+2,799.30</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.98%</t>
+          <t>+2.16%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-0.821</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1623,24 +1623,24 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-0.0077%</t>
+          <t>0.0092%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4.7824%</t>
+          <t>4.9396%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1767,26 +1767,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,010,554.01</t>
+          <t>¥1,032,327.15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+10,554.01</t>
+          <t>¥+32,327.15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>+3.23%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+8.62%</t>
+          <t>+27.50%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.438</v>
+        <v>1.264</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1795,24 +1795,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0414%</t>
+          <t>0.1074%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19.2732%</t>
+          <t>19.8473%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1919,26 +1919,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥999,897.23</t>
+          <t>¥1,013,995.87</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥-102.77</t>
+          <t>¥+13,995.87</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+1.40%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+11.20%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-0.076</v>
+        <v>0.697</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1947,24 +1947,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0036%</t>
+          <t>0.0476%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14.0505%</t>
+          <t>14.3644%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2071,26 +2071,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,003,463.46</t>
+          <t>¥1,015,237.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+3,463.46</t>
+          <t>¥+15,237.23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.76%</t>
+          <t>+12.24%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.133</v>
+        <v>1.007</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2099,24 +2099,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0132%</t>
+          <t>0.0494%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10.0520%</t>
+          <t>10.3997%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2243,26 +2243,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,044,845.94</t>
+          <t>¥1,050,309.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+44,845.94</t>
+          <t>¥+50,309.94</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+4.48%</t>
+          <t>+5.03%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+41.27%</t>
+          <t>+45.47%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.967</v>
+        <v>4.351</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2271,24 +2271,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1431%</t>
+          <t>0.1550%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8.5895%</t>
+          <t>8.5191%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2319,26 +2319,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,020,044.35</t>
+          <t>¥1,030,867.82</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+20,044.35</t>
+          <t>¥+30,867.82</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+2.00%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+16.92%</t>
+          <t>+26.13%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.805</v>
+        <v>2.67</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2347,24 +2347,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0653%</t>
+          <t>0.0964%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8.0199%</t>
+          <t>8.3590%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2395,26 +2395,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,004,929.36</t>
+          <t>¥1,023,654.23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+4,929.36</t>
+          <t>¥+23,654.23</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+2.37%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+3.95%</t>
+          <t>+19.55%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.206</v>
+        <v>1.051</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2423,24 +2423,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0214%</t>
+          <t>0.0789%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16.5132%</t>
+          <t>17.0308%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2547,26 +2547,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,002,361.69</t>
+          <t>¥1,014,715.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+2,361.69</t>
+          <t>¥+14,715.29</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.87%</t>
+          <t>+11.80%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.049</v>
+        <v>0.91</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2575,24 +2575,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0100%</t>
+          <t>0.0482%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10.8078%</t>
+          <t>11.1606%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2719,26 +2719,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥992,161.83</t>
+          <t>¥1,010,898.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥-7,838.17</t>
+          <t>¥+10,898.93</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.01%</t>
+          <t>+8.63%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-0.441</v>
+        <v>0.478</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2747,24 +2747,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.0202%</t>
+          <t>0.0395%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16.0361%</t>
+          <t>16.6408%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2795,26 +2795,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥995,189.39</t>
+          <t>¥997,512.81</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥-4,810.61</t>
+          <t>¥-2,487.19</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.97%</t>
+          <t>-2.00%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-0.191</v>
+        <v>-0.095</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2823,24 +2823,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-0.0079%</t>
+          <t>0.0002%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20.7391%</t>
+          <t>20.4021%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2871,26 +2871,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,001,757.22</t>
+          <t>¥1,012,531.22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+1,757.22</t>
+          <t>¥+12,531.22</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>+9.98%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-0.005</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2899,24 +2899,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0077%</t>
+          <t>0.0410%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10.0141%</t>
+          <t>10.2882%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2947,26 +2947,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥996,835.60</t>
+          <t>¥1,000,956.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥-3,164.40</t>
+          <t>¥+956.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>+0.73%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-1.234</v>
+        <v>-0.307</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2975,24 +2975,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.0100%</t>
+          <t>0.0033%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3.6381%</t>
+          <t>3.7668%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -3023,26 +3023,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥997,466.80</t>
+          <t>¥1,002,799.30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥-2,533.20</t>
+          <t>¥+2,799.30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.98%</t>
+          <t>+2.16%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-0.821</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3051,24 +3051,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.0077%</t>
+          <t>0.0092%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>4.7824%</t>
+          <t>4.9396%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>

--- a/performance-dashboard/reports/daily/交易表现分析.xlsx
+++ b/performance-dashboard/reports/daily/交易表现分析.xlsx
@@ -11,6 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模式1-纯数据" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模式2-数据+技术" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模式3-数据+新闻" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模式4-多智能体" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模式5-巴菲特" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,26 +609,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,031,521.13</t>
+          <t>¥1,049,011.17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+31,521.13</t>
+          <t>¥+49,011.17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+3.15%</t>
+          <t>+4.90%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+27.69%</t>
+          <t>+44.11%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.337</v>
+        <v>1.981</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,24 +637,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1072%</t>
+          <t>0.1569%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18.7317%</t>
+          <t>18.9515%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -661,7 +663,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -759,26 +761,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥997,597.22</t>
+          <t>¥1,013,117.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥-2,402.78</t>
+          <t>¥+13,117.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>+10.46%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-0.309</v>
+        <v>0.779</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -787,24 +789,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.0054%</t>
+          <t>0.0434%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10.8126%</t>
+          <t>11.4827%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -813,7 +815,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1139,26 +1141,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>¥1,041,871.47</t>
+          <t>¥1,068,188.97</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>¥+41,871.47</t>
+          <t>¥+68,188.97</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+4.19%</t>
+          <t>+6.82%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+38.13%</t>
+          <t>+65.49%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.476</v>
+        <v>2.232</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1167,24 +1169,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.1432%</t>
+          <t>0.2177%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>23.1144%</t>
+          <t>23.6832%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1193,7 +1195,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1648,6 +1650,462 @@
         </is>
       </c>
       <c r="P16" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>模式4-多智能体</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>multi-agent</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>¥1,040,969.99</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>¥+40,969.99</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>+4.10%</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>+37.19%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>2.433</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3.10%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>51.6%</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.1330%</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>12.9580%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>32</v>
+      </c>
+      <c r="N17" t="n">
+        <v>32</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>deepseek-v3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>¥1,163,418.90</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>¥+163,418.90</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>+16.34%</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>+229.36%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>11.676</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>80.6%</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.4916%</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>10.4408%</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>32</v>
+      </c>
+      <c r="N18" t="n">
+        <v>32</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>gemini-3-pro</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>¥1,191,654.11</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>¥+191,654.11</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>+19.17%</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>+297.82%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>12.188</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>90.3%</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0.5699%</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>11.6204%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>32</v>
+      </c>
+      <c r="N19" t="n">
+        <v>32</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>gpt-5</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>¥1,324,359.42</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>¥+324,359.42</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>+32.44%</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>+813.68%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>18.525</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>90.3%</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0.9133%</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>12.3172%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>32</v>
+      </c>
+      <c r="N20" t="n">
+        <v>32</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>llama-3.1-405b</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>¥1,220,109.37</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>¥+220,109.37</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>+22.01%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>+379.06%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>9.349</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>83.9%</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0.6496%</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>17.2990%</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>32</v>
+      </c>
+      <c r="N21" t="n">
+        <v>32</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>qwen-72b</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>¥1,521,805.19</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>¥+521,805.19</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>+52.18%</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>+2629.47%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>18.973</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>90.3%</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1.3701%</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>18.0926%</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>32</v>
+      </c>
+      <c r="N22" t="n">
+        <v>32</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>20260203</t>
         </is>
@@ -1843,26 +2301,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,031,521.13</t>
+          <t>¥1,049,011.17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+31,521.13</t>
+          <t>¥+49,011.17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+3.15%</t>
+          <t>+4.90%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+27.69%</t>
+          <t>+44.11%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.337</v>
+        <v>1.981</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1871,24 +2329,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1072%</t>
+          <t>0.1569%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18.7317%</t>
+          <t>18.9515%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -1897,7 +2355,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -1995,26 +2453,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥997,597.22</t>
+          <t>¥1,013,117.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥-2,402.78</t>
+          <t>¥+13,117.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>+10.46%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-0.309</v>
+        <v>0.779</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2023,24 +2481,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.0054%</t>
+          <t>0.0434%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10.8126%</t>
+          <t>11.4827%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2049,7 +2507,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -2471,26 +2929,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,041,871.47</t>
+          <t>¥1,068,188.97</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+41,871.47</t>
+          <t>¥+68,188.97</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+4.19%</t>
+          <t>+6.82%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+38.13%</t>
+          <t>+65.49%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.476</v>
+        <v>2.232</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2499,24 +2957,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.1432%</t>
+          <t>0.2177%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>23.1144%</t>
+          <t>23.6832%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2525,7 +2983,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260202</t>
+          <t>20260203</t>
         </is>
       </c>
     </row>
@@ -3084,4 +3542,652 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>模式</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>初始资金</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>最新资金</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>总利润</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>总收益率(%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>年化收益率(%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>夏普比率</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>最大回撤(%)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>胜率(%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>日均收益率(%)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>年化波动率(%)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>交易日数</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>文件数量</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>分析日期</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>数据日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>模式4-多智能体</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>multi-agent</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>¥1,040,969.99</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>¥+40,969.99</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>+4.10%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>+37.19%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2.433</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3.10%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>51.6%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.1330%</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>12.9580%</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>模式</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>初始资金</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>最新资金</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>总利润</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>总收益率(%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>年化收益率(%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>夏普比率</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>最大回撤(%)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>胜率(%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>日均收益率(%)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>年化波动率(%)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>交易日数</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>文件数量</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>分析日期</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>数据日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>deepseek-v3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>¥1,163,418.90</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>¥+163,418.90</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>+16.34%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>+229.36%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>11.676</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>80.6%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.4916%</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10.4408%</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>gemini-3-pro</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>¥1,191,654.11</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>¥+191,654.11</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>+19.17%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>+297.82%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>12.188</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>90.3%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.5699%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>11.6204%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>32</v>
+      </c>
+      <c r="N3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>gpt-5</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>¥1,324,359.42</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>¥+324,359.42</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>+32.44%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>+813.68%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>18.525</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>90.3%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.9133%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>12.3172%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>32</v>
+      </c>
+      <c r="N4" t="n">
+        <v>32</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>llama-3.1-405b</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>¥1,220,109.37</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>¥+220,109.37</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>+22.01%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>+379.06%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>9.349</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>83.9%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.6496%</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>17.2990%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>32</v>
+      </c>
+      <c r="N5" t="n">
+        <v>32</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>模式5-巴菲特</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>qwen-72b</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>¥1,000,000.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>¥1,521,805.19</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>¥+521,805.19</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>+52.18%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>+2629.47%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>18.973</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>90.3%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1.3701%</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>18.0926%</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>32</v>
+      </c>
+      <c r="N6" t="n">
+        <v>32</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/performance-dashboard/reports/daily/交易表现分析.xlsx
+++ b/performance-dashboard/reports/daily/交易表现分析.xlsx
@@ -685,26 +685,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥999,628.52</t>
+          <t>¥1,003,344.12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥-371.48</t>
+          <t>¥+3,344.12</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>+11.09%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-2.448</v>
+        <v>4.049</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -713,24 +713,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-0.0062%</t>
+          <t>0.0478%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.4424%</t>
+          <t>2.4877%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260213</t>
+          <t>20260224</t>
         </is>
       </c>
     </row>
@@ -2377,26 +2377,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥999,628.52</t>
+          <t>¥1,003,344.12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥-371.48</t>
+          <t>¥+3,344.12</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.33%</t>
+          <t>+11.09%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-2.448</v>
+        <v>4.049</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2405,24 +2405,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-0.0062%</t>
+          <t>0.0478%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.4424%</t>
+          <t>2.4877%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260213</t>
+          <t>20260224</t>
         </is>
       </c>
     </row>

--- a/performance-dashboard/reports/daily/交易表现分析.xlsx
+++ b/performance-dashboard/reports/daily/交易表现分析.xlsx
@@ -989,26 +989,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>¥1,008,159.44</t>
+          <t>¥1,021,059.58</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>¥+8,159.44</t>
+          <t>¥+21,059.58</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>+2.11%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+33.98%</t>
+          <t>+92.80%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4.799</v>
+        <v>8.255000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1017,24 +1017,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.1364%</t>
+          <t>0.2997%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6.7517%</t>
+          <t>8.9105%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>20260213</t>
+          <t>20260224</t>
         </is>
       </c>
     </row>
@@ -2777,26 +2777,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,008,159.44</t>
+          <t>¥1,021,059.58</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+8,159.44</t>
+          <t>¥+21,059.58</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>+2.11%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+33.98%</t>
+          <t>+92.80%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4.799</v>
+        <v>8.255000000000001</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2805,24 +2805,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1364%</t>
+          <t>0.2997%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6.7517%</t>
+          <t>8.9105%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260213</t>
+          <t>20260224</t>
         </is>
       </c>
     </row>

--- a/performance-dashboard/reports/daily/交易表现分析.xlsx
+++ b/performance-dashboard/reports/daily/交易表现分析.xlsx
@@ -533,26 +533,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,007,955.70</t>
+          <t>¥1,006,745.44</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+7,955.70</t>
+          <t>¥+6,745.44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.80%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+24.84%</t>
+          <t>+18.46%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4.494</v>
+        <v>3.413</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -561,24 +561,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0996%</t>
+          <t>0.0752%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5.1456%</t>
+          <t>4.9736%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -609,26 +609,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,012,414.32</t>
+          <t>¥1,012,319.30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+12,414.32</t>
+          <t>¥+12,319.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.24%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+41.26%</t>
+          <t>+36.14%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.984</v>
+        <v>2.766</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -637,24 +637,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1575%</t>
+          <t>0.1390%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12.6378%</t>
+          <t>11.9441%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -685,26 +685,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,003,867.32</t>
+          <t>¥1,002,904.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+3,867.32</t>
+          <t>¥+2,904.72</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+11.41%</t>
+          <t>+7.58%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4.387</v>
+        <v>2.672</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -713,24 +713,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0484%</t>
+          <t>0.0323%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.3272%</t>
+          <t>2.3091%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -761,26 +761,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,005,355.08</t>
+          <t>¥1,004,162.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+5,355.08</t>
+          <t>¥+4,162.48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.54%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+16.13%</t>
+          <t>+11.04%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3.63</v>
+        <v>2.441</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -789,24 +789,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0671%</t>
+          <t>0.0465%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4.1133%</t>
+          <t>3.9872%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -837,52 +837,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,003,522.76</t>
+          <t>¥1,000,089.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+3,522.76</t>
+          <t>¥+89.36</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+10.35%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.918</v>
+        <v>-0.473</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0442%</t>
+          <t>0.0012%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3.1350%</t>
+          <t>3.5285%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -913,26 +913,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>¥1,009,283.84</t>
+          <t>¥1,007,917.87</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>¥+9,283.84</t>
+          <t>¥+7,917.87</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+29.53%</t>
+          <t>+21.99%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6.053</v>
+        <v>4.567</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -941,24 +941,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.1160%</t>
+          <t>0.0881%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4.5012%</t>
+          <t>4.4251%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -989,26 +989,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>¥1,024,989.53</t>
+          <t>¥1,023,966.21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>¥+24,989.53</t>
+          <t>¥+23,966.21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.50%</t>
+          <t>+2.40%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+99.59%</t>
+          <t>+81.63%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>9.132999999999999</v>
+        <v>7.963</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1017,24 +1017,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.3104%</t>
+          <t>0.2648%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8.3470%</t>
+          <t>8.1314%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1065,26 +1065,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>¥1,010,819.86</t>
+          <t>¥1,009,096.75</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>¥+10,819.86</t>
+          <t>¥+9,096.75</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+35.17%</t>
+          <t>+25.63%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4.214</v>
+        <v>3.21</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1093,24 +1093,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.1358%</t>
+          <t>0.1017%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>7.6483%</t>
+          <t>7.3709%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1141,26 +1141,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>¥1,012,917.46</t>
+          <t>¥1,011,569.49</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>¥+12,917.46</t>
+          <t>¥+11,569.49</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1.29%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+43.24%</t>
+          <t>+33.63%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>10.685</v>
+        <v>8.186</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1169,24 +1169,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.1608%</t>
+          <t>0.1282%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3.6075%</t>
+          <t>3.7038%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1217,26 +1217,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>¥1,022,896.42</t>
+          <t>¥1,020,640.23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>¥+22,896.42</t>
+          <t>¥+20,640.23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+2.06%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+88.49%</t>
+          <t>+67.34%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>9.382</v>
+        <v>7.464</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1245,24 +1245,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.2845%</t>
+          <t>0.2284%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>7.4296%</t>
+          <t>7.4440%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1293,26 +1293,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>¥1,008,287.74</t>
+          <t>¥1,006,718.44</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>¥+8,287.74</t>
+          <t>¥+6,718.44</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+26.00%</t>
+          <t>+18.38%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4.649</v>
+        <v>3.335</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1321,24 +1321,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.1038%</t>
+          <t>0.0749%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>5.1978%</t>
+          <t>5.0685%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1369,26 +1369,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>¥1,012,215.45</t>
+          <t>¥1,010,687.79</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>¥+12,215.45</t>
+          <t>¥+10,687.79</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+40.49%</t>
+          <t>+30.72%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7.996</v>
+        <v>6.133</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1397,24 +1397,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.1523%</t>
+          <t>0.1186%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4.5521%</t>
+          <t>4.5506%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1445,26 +1445,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>¥1,014,001.52</t>
+          <t>¥1,015,216.12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>¥+14,001.52</t>
+          <t>¥+15,216.12</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+1.40%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+47.60%</t>
+          <t>+46.31%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8.162000000000001</v>
+        <v>8.329000000000001</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1473,24 +1473,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.1745%</t>
+          <t>0.1684%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>5.1441%</t>
+          <t>4.8576%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>¥999,962.00</t>
+          <t>¥999,955.30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>¥-38.00</t>
+          <t>¥-44.70</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-1353.68</v>
+        <v>-1198.58</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1559,14 +1559,14 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.0016%</t>
+          <t>0.0018%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1597,52 +1597,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>¥1,000,238.51</t>
+          <t>¥999,913.51</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>¥+238.51</t>
+          <t>¥-86.49</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-10.954</v>
+        <v>-10.779</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.0030%</t>
+          <t>-0.0010%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.1122%</t>
+          <t>0.2062%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1673,26 +1673,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>¥1,004,682.22</t>
+          <t>¥1,006,642.72</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>¥+4,682.22</t>
+          <t>¥+6,642.72</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+13.97%</t>
+          <t>+18.16%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.371</v>
+        <v>3.231</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1701,24 +1701,24 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.0590%</t>
+          <t>0.0741%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>5.4340%</t>
+          <t>5.1680%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>¥1,014,807.05</t>
+          <t>¥1,020,166.25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>¥+14,807.05</t>
+          <t>¥+20,166.25</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+1.48%</t>
+          <t>+2.02%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+50.92%</t>
+          <t>+65.39%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>11.055</v>
+        <v>12.997</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1777,24 +1777,24 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.1842%</t>
+          <t>0.2224%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>4.0201%</t>
+          <t>4.1604%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1825,26 +1825,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>¥1,061,603.19</t>
+          <t>¥1,072,892.19</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>¥+61,603.19</t>
+          <t>¥+72,892.19</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>+7.29%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+433.26%</t>
+          <t>+488.86%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>34.323</v>
+        <v>36.466</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1853,24 +1853,24 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.7506%</t>
+          <t>0.7854%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5.4535%</t>
+          <t>5.3731%</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1901,26 +1901,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>¥1,006,301.78</t>
+          <t>¥1,008,010.58</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>¥+6,301.78</t>
+          <t>¥+8,010.58</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>+0.80%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+19.23%</t>
+          <t>+22.27%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>17.793</v>
+        <v>19.438</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1929,24 +1929,24 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.0786%</t>
+          <t>0.0887%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.0015%</t>
+          <t>1.0482%</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1977,26 +1977,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>¥1,061,631.42</t>
+          <t>¥1,075,046.22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>¥+61,631.42</t>
+          <t>¥+75,046.22</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>+7.50%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+433.66%</t>
+          <t>+519.39%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>28.498</v>
+        <v>30.083</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2005,24 +2005,24 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.7512%</t>
+          <t>0.8082%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>6.5736%</t>
+          <t>6.7041%</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2053,26 +2053,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>¥1,062,825.52</t>
+          <t>¥1,077,526.32</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>¥+62,825.52</t>
+          <t>¥+77,526.32</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+6.28%</t>
+          <t>+7.75%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+450.73%</t>
+          <t>+556.42%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>24.846</v>
+        <v>26.449</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2081,24 +2081,24 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.7657%</t>
+          <t>0.8343%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>7.6864%</t>
+          <t>7.8743%</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2225,26 +2225,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,007,955.70</t>
+          <t>¥1,006,745.44</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+7,955.70</t>
+          <t>¥+6,745.44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.80%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+24.84%</t>
+          <t>+18.46%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4.494</v>
+        <v>3.413</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2253,24 +2253,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0996%</t>
+          <t>0.0752%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5.1456%</t>
+          <t>4.9736%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2301,26 +2301,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,012,414.32</t>
+          <t>¥1,012,319.30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+12,414.32</t>
+          <t>¥+12,319.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.24%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+41.26%</t>
+          <t>+36.14%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.984</v>
+        <v>2.766</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2329,24 +2329,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1575%</t>
+          <t>0.1390%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12.6378%</t>
+          <t>11.9441%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2377,26 +2377,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,003,867.32</t>
+          <t>¥1,002,904.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+3,867.32</t>
+          <t>¥+2,904.72</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+11.41%</t>
+          <t>+7.58%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4.387</v>
+        <v>2.672</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2405,24 +2405,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0484%</t>
+          <t>0.0323%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.3272%</t>
+          <t>2.3091%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2453,26 +2453,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,005,355.08</t>
+          <t>¥1,004,162.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+5,355.08</t>
+          <t>¥+4,162.48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.54%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+16.13%</t>
+          <t>+11.04%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3.63</v>
+        <v>2.441</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2481,24 +2481,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0671%</t>
+          <t>0.0465%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4.1133%</t>
+          <t>3.9872%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2529,52 +2529,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,003,522.76</t>
+          <t>¥1,000,089.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+3,522.76</t>
+          <t>¥+89.36</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+10.35%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.918</v>
+        <v>-0.473</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0442%</t>
+          <t>0.0012%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3.1350%</t>
+          <t>3.5285%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2701,26 +2701,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,009,283.84</t>
+          <t>¥1,007,917.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+9,283.84</t>
+          <t>¥+7,917.87</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+29.53%</t>
+          <t>+21.99%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6.053</v>
+        <v>4.567</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2729,24 +2729,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1160%</t>
+          <t>0.0881%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4.5012%</t>
+          <t>4.4251%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2777,26 +2777,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,024,989.53</t>
+          <t>¥1,023,966.21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+24,989.53</t>
+          <t>¥+23,966.21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+2.50%</t>
+          <t>+2.40%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+99.59%</t>
+          <t>+81.63%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>9.132999999999999</v>
+        <v>7.963</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2805,24 +2805,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.3104%</t>
+          <t>0.2648%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8.3470%</t>
+          <t>8.1314%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2853,26 +2853,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,010,819.86</t>
+          <t>¥1,009,096.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+10,819.86</t>
+          <t>¥+9,096.75</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+35.17%</t>
+          <t>+25.63%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4.214</v>
+        <v>3.21</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2881,24 +2881,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.1358%</t>
+          <t>0.1017%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>7.6483%</t>
+          <t>7.3709%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2929,26 +2929,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,012,917.46</t>
+          <t>¥1,011,569.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+12,917.46</t>
+          <t>¥+11,569.49</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+1.29%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+43.24%</t>
+          <t>+33.63%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>10.685</v>
+        <v>8.186</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2957,24 +2957,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.1608%</t>
+          <t>0.1282%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3.6075%</t>
+          <t>3.7038%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3005,26 +3005,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,022,896.42</t>
+          <t>¥1,020,640.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+22,896.42</t>
+          <t>¥+20,640.23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+2.06%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+88.49%</t>
+          <t>+67.34%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>9.382</v>
+        <v>7.464</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3033,24 +3033,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.2845%</t>
+          <t>0.2284%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>7.4296%</t>
+          <t>7.4440%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3177,26 +3177,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,008,287.74</t>
+          <t>¥1,006,718.44</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+8,287.74</t>
+          <t>¥+6,718.44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+26.00%</t>
+          <t>+18.38%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4.649</v>
+        <v>3.335</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3205,24 +3205,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1038%</t>
+          <t>0.0749%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5.1978%</t>
+          <t>5.0685%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3253,26 +3253,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,012,215.45</t>
+          <t>¥1,010,687.79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+12,215.45</t>
+          <t>¥+10,687.79</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+40.49%</t>
+          <t>+30.72%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>7.996</v>
+        <v>6.133</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3281,24 +3281,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1523%</t>
+          <t>0.1186%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4.5521%</t>
+          <t>4.5506%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3329,26 +3329,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,014,001.52</t>
+          <t>¥1,015,216.12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+14,001.52</t>
+          <t>¥+15,216.12</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.40%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+47.60%</t>
+          <t>+46.31%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.162000000000001</v>
+        <v>8.329000000000001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -3357,24 +3357,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.1745%</t>
+          <t>0.1684%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5.1441%</t>
+          <t>4.8576%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3405,12 +3405,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥999,962.00</t>
+          <t>¥999,955.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥-38.00</t>
+          <t>¥-44.70</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-1353.68</v>
+        <v>-1198.58</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -3443,14 +3443,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.0016%</t>
+          <t>0.0018%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3481,52 +3481,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,000,238.51</t>
+          <t>¥999,913.51</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+238.51</t>
+          <t>¥-86.49</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-10.954</v>
+        <v>-10.779</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0030%</t>
+          <t>-0.0010%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.1122%</t>
+          <t>0.2062%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3653,26 +3653,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,004,682.22</t>
+          <t>¥1,006,642.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+4,682.22</t>
+          <t>¥+6,642.72</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+13.97%</t>
+          <t>+18.16%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2.371</v>
+        <v>3.231</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3681,24 +3681,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0590%</t>
+          <t>0.0741%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5.4340%</t>
+          <t>5.1680%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3825,26 +3825,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,014,807.05</t>
+          <t>¥1,020,166.25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+14,807.05</t>
+          <t>¥+20,166.25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.48%</t>
+          <t>+2.02%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+50.92%</t>
+          <t>+65.39%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>11.055</v>
+        <v>12.997</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3853,24 +3853,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1842%</t>
+          <t>0.2224%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4.0201%</t>
+          <t>4.1604%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3901,26 +3901,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,061,603.19</t>
+          <t>¥1,072,892.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+61,603.19</t>
+          <t>¥+72,892.19</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>+7.29%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+433.26%</t>
+          <t>+488.86%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>34.323</v>
+        <v>36.466</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3929,24 +3929,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.7506%</t>
+          <t>0.7854%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5.4535%</t>
+          <t>5.3731%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3977,26 +3977,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,006,301.78</t>
+          <t>¥1,008,010.58</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+6,301.78</t>
+          <t>¥+8,010.58</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>+0.80%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+19.23%</t>
+          <t>+22.27%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>17.793</v>
+        <v>19.438</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -4005,24 +4005,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0786%</t>
+          <t>0.0887%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.0015%</t>
+          <t>1.0482%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -4053,26 +4053,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,061,631.42</t>
+          <t>¥1,075,046.22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+61,631.42</t>
+          <t>¥+75,046.22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>+7.50%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+433.66%</t>
+          <t>+519.39%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28.498</v>
+        <v>30.083</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -4081,24 +4081,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.7512%</t>
+          <t>0.8082%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>6.5736%</t>
+          <t>6.7041%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -4129,26 +4129,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,062,825.52</t>
+          <t>¥1,077,526.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+62,825.52</t>
+          <t>¥+77,526.32</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+6.28%</t>
+          <t>+7.75%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+450.73%</t>
+          <t>+556.42%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>24.846</v>
+        <v>26.449</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -4157,24 +4157,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.7657%</t>
+          <t>0.8343%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>7.6864%</t>
+          <t>7.8743%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>

--- a/performance-dashboard/reports/daily/交易表现分析.xlsx
+++ b/performance-dashboard/reports/daily/交易表现分析.xlsx
@@ -1673,52 +1673,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>¥989,672.84</t>
+          <t>¥988,948.10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>¥-10,327.16</t>
+          <t>¥-11,051.90</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-17.04%</t>
+          <t>-17.03%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-2.051</v>
+        <v>-2.121</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.69%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-0.0776%</t>
+          <t>-0.0773%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>10.5014%</t>
+          <t>10.1194%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>20260304</t>
+          <t>20260305</t>
         </is>
       </c>
     </row>
@@ -3653,52 +3653,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥989,672.84</t>
+          <t>¥988,948.10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥-10,327.16</t>
+          <t>¥-11,051.90</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-17.04%</t>
+          <t>-17.03%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-2.051</v>
+        <v>-2.121</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.69%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.0776%</t>
+          <t>-0.0773%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10.5014%</t>
+          <t>10.1194%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260304</t>
+          <t>20260305</t>
         </is>
       </c>
     </row>

--- a/performance-dashboard/reports/daily/交易表现分析.xlsx
+++ b/performance-dashboard/reports/daily/交易表现分析.xlsx
@@ -533,26 +533,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,003,008.57</t>
+          <t>¥1,013,310.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+3,008.57</t>
+          <t>¥+13,310.87</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+1.33%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+4.30%</t>
+          <t>+19.17%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.374</v>
+        <v>2.107</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -561,24 +561,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0187%</t>
+          <t>0.0748%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7.3180%</t>
+          <t>8.0015%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -609,26 +609,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,018,121.62</t>
+          <t>¥1,027,056.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+18,121.62</t>
+          <t>¥+27,056.98</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.81%</t>
+          <t>+2.71%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+28.59%</t>
+          <t>+42.49%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.948</v>
+        <v>2.784</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -637,24 +637,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1091%</t>
+          <t>0.1518%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13.0934%</t>
+          <t>13.0278%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -685,26 +685,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,003,192.72</t>
+          <t>¥1,017,795.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+3,192.72</t>
+          <t>¥+17,795.74</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+1.78%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+4.56%</t>
+          <t>+26.36%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.661</v>
+        <v>3.432</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -713,24 +713,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0191%</t>
+          <t>0.0989%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4.2952%</t>
+          <t>6.6866%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -761,26 +761,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,009,825.68</t>
+          <t>¥1,012,616.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+9,825.68</t>
+          <t>¥+12,616.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>+1.26%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+14.67%</t>
+          <t>+18.09%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.312</v>
+        <v>2.92</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -789,24 +789,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0581%</t>
+          <t>0.0703%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5.4799%</t>
+          <t>5.3843%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -837,26 +837,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥988,498.15</t>
+          <t>¥990,085.88</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥-11,501.85</t>
+          <t>¥-9,914.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-14.95%</t>
+          <t>-12.38%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-2.138</v>
+        <v>-1.818</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -865,24 +865,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.0665%</t>
+          <t>-0.0539%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8.7655%</t>
+          <t>8.5585%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -913,26 +913,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>¥1,015,332.99</t>
+          <t>¥1,017,331.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>¥+15,332.99</t>
+          <t>¥+17,331.69</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+23.74%</t>
+          <t>+25.60%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3.857</v>
+        <v>4.243</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -941,24 +941,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.0901%</t>
+          <t>0.0961%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>5.3750%</t>
+          <t>5.2380%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -989,26 +989,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>¥1,025,690.35</t>
+          <t>¥1,025,292.99</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>¥+25,690.35</t>
+          <t>¥+25,292.99</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.57%</t>
+          <t>+2.53%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+42.64%</t>
+          <t>+39.28%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.108</v>
+        <v>4.845</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1017,24 +1017,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.1503%</t>
+          <t>0.1398%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>7.0265%</t>
+          <t>6.8630%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1065,26 +1065,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>¥1,024,543.77</t>
+          <t>¥1,029,419.77</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>¥+24,543.77</t>
+          <t>¥+29,419.77</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>+2.94%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+40.42%</t>
+          <t>+46.90%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3.908</v>
+        <v>4.52</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1093,24 +1093,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.1443%</t>
+          <t>0.1627%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8.7960%</t>
+          <t>8.6328%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1141,26 +1141,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>¥1,025,844.39</t>
+          <t>¥1,032,583.39</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>¥+25,844.39</t>
+          <t>¥+32,583.39</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+2.58%</t>
+          <t>+3.26%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+42.94%</t>
+          <t>+53.00%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6.584</v>
+        <v>7.662</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1169,24 +1169,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.1508%</t>
+          <t>0.1789%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5.4707%</t>
+          <t>5.6261%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1217,26 +1217,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>¥1,029,984.76</t>
+          <t>¥1,033,468.02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>¥+29,984.76</t>
+          <t>¥+33,468.02</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+3.00%</t>
+          <t>+3.35%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+51.23%</t>
+          <t>+54.75%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4.225</v>
+        <v>4.572</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1245,24 +1245,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.1759%</t>
+          <t>0.1849%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10.0247%</t>
+          <t>9.7602%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1293,26 +1293,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>¥1,004,255.66</t>
+          <t>¥1,011,153.45</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>¥+4,255.66</t>
+          <t>¥+11,153.45</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+1.12%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+6.13%</t>
+          <t>+15.85%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.605</v>
+        <v>1.782</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1321,24 +1321,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.0261%</t>
+          <t>0.0628%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>7.6106%</t>
+          <t>7.7766%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1369,26 +1369,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>¥1,001,879.24</t>
+          <t>¥1,012,150.64</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>¥+1,879.24</t>
+          <t>¥+12,150.64</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+1.22%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+2.66%</t>
+          <t>+17.37%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.131</v>
+        <v>1.523</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1397,24 +1397,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.0129%</t>
+          <t>0.0692%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>9.7295%</t>
+          <t>10.1466%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1445,26 +1445,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>¥1,008,533.49</t>
+          <t>¥1,017,234.07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>¥+8,533.49</t>
+          <t>¥+17,234.07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+12.63%</t>
+          <t>+25.44%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.431</v>
+        <v>2.793</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1473,24 +1473,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.0512%</t>
+          <t>0.0962%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7.6233%</t>
+          <t>7.9746%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>¥999,273.30</t>
+          <t>¥999,306.30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>¥-726.70</t>
+          <t>¥-693.70</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1536,11 +1536,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-11.13</v>
+        <v>-10.997</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1549,24 +1549,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-0.0043%</t>
+          <t>-0.0039%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.2747%</t>
+          <t>0.2684%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1597,26 +1597,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>¥999,412.03</t>
+          <t>¥999,786.03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>¥-587.97</t>
+          <t>¥-213.97</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.82%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-2.72</v>
+        <v>-2.213</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1625,24 +1625,24 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-0.0034%</t>
+          <t>-0.0012%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.0467%</t>
+          <t>1.0280%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1673,26 +1673,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>¥979,208.46</t>
+          <t>¥992,699.32</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>¥-20,791.54</t>
+          <t>¥-7,300.68</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.08%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-25.48%</t>
+          <t>-9.26%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-2.841</v>
+        <v>-0.927</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1701,24 +1701,24 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-0.1209%</t>
+          <t>-0.0377%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>11.4230%</t>
+          <t>12.3666%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>¥1,008,890.44</t>
+          <t>¥1,010,094.44</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>¥+8,890.44</t>
+          <t>¥+10,094.44</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+13.19%</t>
+          <t>+14.25%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.869</v>
+        <v>2.08</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1777,24 +1777,24 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.0528%</t>
+          <t>0.0565%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>6.0600%</t>
+          <t>5.8942%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1825,26 +1825,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>¥1,006,861.48</t>
+          <t>¥1,008,315.28</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>¥+6,861.48</t>
+          <t>¥+8,315.28</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+10.05%</t>
+          <t>+11.61%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.55</v>
+        <v>1.868</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1853,24 +1853,24 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.0408%</t>
+          <t>0.0466%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5.3576%</t>
+          <t>5.2202%</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1901,26 +1901,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>¥1,007,817.21</t>
+          <t>¥1,009,244.51</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>¥+7,817.21</t>
+          <t>¥+9,244.51</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+11.52%</t>
+          <t>+12.98%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1.634</v>
+        <v>1.908</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1929,24 +1929,24 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.0465%</t>
+          <t>0.0518%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5.9626%</t>
+          <t>5.8050%</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1977,26 +1977,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>¥1,025,245.55</t>
+          <t>¥1,030,200.75</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>¥+25,245.55</t>
+          <t>¥+30,200.75</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+2.52%</t>
+          <t>+3.02%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+41.77%</t>
+          <t>+48.38%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6.364</v>
+        <v>7.239</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2005,24 +2005,24 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.1474%</t>
+          <t>0.1660%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>5.5247%</t>
+          <t>5.5063%</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2053,26 +2053,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>¥1,029,043.50</t>
+          <t>¥1,030,515.20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>¥+29,043.50</t>
+          <t>¥+30,515.20</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+2.90%</t>
+          <t>+3.05%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+49.30%</t>
+          <t>+48.99%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3.657</v>
+        <v>3.727</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2081,24 +2081,24 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.1710%</t>
+          <t>0.1695%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>11.2452%</t>
+          <t>10.9288%</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2225,26 +2225,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,003,008.57</t>
+          <t>¥1,013,310.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+3,008.57</t>
+          <t>¥+13,310.87</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+1.33%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+4.30%</t>
+          <t>+19.17%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.374</v>
+        <v>2.107</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2253,24 +2253,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0187%</t>
+          <t>0.0748%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7.3180%</t>
+          <t>8.0015%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2301,26 +2301,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,018,121.62</t>
+          <t>¥1,027,056.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+18,121.62</t>
+          <t>¥+27,056.98</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.81%</t>
+          <t>+2.71%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+28.59%</t>
+          <t>+42.49%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.948</v>
+        <v>2.784</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2329,24 +2329,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1091%</t>
+          <t>0.1518%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13.0934%</t>
+          <t>13.0278%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2377,26 +2377,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,003,192.72</t>
+          <t>¥1,017,795.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+3,192.72</t>
+          <t>¥+17,795.74</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+1.78%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+4.56%</t>
+          <t>+26.36%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.661</v>
+        <v>3.432</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2405,24 +2405,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0191%</t>
+          <t>0.0989%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4.2952%</t>
+          <t>6.6866%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2453,26 +2453,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,009,825.68</t>
+          <t>¥1,012,616.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+9,825.68</t>
+          <t>¥+12,616.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>+1.26%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+14.67%</t>
+          <t>+18.09%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.312</v>
+        <v>2.92</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2481,24 +2481,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0581%</t>
+          <t>0.0703%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5.4799%</t>
+          <t>5.3843%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2529,26 +2529,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥988,498.15</t>
+          <t>¥990,085.88</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥-11,501.85</t>
+          <t>¥-9,914.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-14.95%</t>
+          <t>-12.38%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-2.138</v>
+        <v>-1.818</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2557,24 +2557,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.0665%</t>
+          <t>-0.0539%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8.7655%</t>
+          <t>8.5585%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2701,26 +2701,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,015,332.99</t>
+          <t>¥1,017,331.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+15,332.99</t>
+          <t>¥+17,331.69</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+23.74%</t>
+          <t>+25.60%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.857</v>
+        <v>4.243</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2729,24 +2729,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0901%</t>
+          <t>0.0961%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5.3750%</t>
+          <t>5.2380%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2777,26 +2777,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,025,690.35</t>
+          <t>¥1,025,292.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+25,690.35</t>
+          <t>¥+25,292.99</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+2.57%</t>
+          <t>+2.53%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+42.64%</t>
+          <t>+39.28%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5.108</v>
+        <v>4.845</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2805,24 +2805,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1503%</t>
+          <t>0.1398%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7.0265%</t>
+          <t>6.8630%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2853,26 +2853,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,024,543.77</t>
+          <t>¥1,029,419.77</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+24,543.77</t>
+          <t>¥+29,419.77</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>+2.94%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+40.42%</t>
+          <t>+46.90%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3.908</v>
+        <v>4.52</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2881,24 +2881,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.1443%</t>
+          <t>0.1627%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8.7960%</t>
+          <t>8.6328%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2929,26 +2929,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,025,844.39</t>
+          <t>¥1,032,583.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+25,844.39</t>
+          <t>¥+32,583.39</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+2.58%</t>
+          <t>+3.26%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+42.94%</t>
+          <t>+53.00%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6.584</v>
+        <v>7.662</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2957,24 +2957,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.1508%</t>
+          <t>0.1789%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5.4707%</t>
+          <t>5.6261%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3005,26 +3005,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,029,984.76</t>
+          <t>¥1,033,468.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+29,984.76</t>
+          <t>¥+33,468.02</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+3.00%</t>
+          <t>+3.35%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+51.23%</t>
+          <t>+54.75%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4.225</v>
+        <v>4.572</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3033,24 +3033,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.1759%</t>
+          <t>0.1849%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10.0247%</t>
+          <t>9.7602%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3177,26 +3177,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,004,255.66</t>
+          <t>¥1,011,153.45</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+4,255.66</t>
+          <t>¥+11,153.45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+1.12%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+6.13%</t>
+          <t>+15.85%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.605</v>
+        <v>1.782</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3205,24 +3205,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0261%</t>
+          <t>0.0628%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7.6106%</t>
+          <t>7.7766%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3253,26 +3253,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,001,879.24</t>
+          <t>¥1,012,150.64</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+1,879.24</t>
+          <t>¥+12,150.64</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+1.22%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+2.66%</t>
+          <t>+17.37%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.131</v>
+        <v>1.523</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3281,24 +3281,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0129%</t>
+          <t>0.0692%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>9.7295%</t>
+          <t>10.1466%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3329,26 +3329,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,008,533.49</t>
+          <t>¥1,017,234.07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+8,533.49</t>
+          <t>¥+17,234.07</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+12.63%</t>
+          <t>+25.44%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.431</v>
+        <v>2.793</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -3357,24 +3357,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0512%</t>
+          <t>0.0962%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>7.6233%</t>
+          <t>7.9746%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3405,12 +3405,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥999,273.30</t>
+          <t>¥999,306.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥-726.70</t>
+          <t>¥-693.70</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3420,11 +3420,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-11.13</v>
+        <v>-10.997</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -3433,24 +3433,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.0043%</t>
+          <t>-0.0039%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.2747%</t>
+          <t>0.2684%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3481,26 +3481,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥999,412.03</t>
+          <t>¥999,786.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥-587.97</t>
+          <t>¥-213.97</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.82%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-2.72</v>
+        <v>-2.213</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3509,24 +3509,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.0034%</t>
+          <t>-0.0012%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.0467%</t>
+          <t>1.0280%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3653,26 +3653,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥979,208.46</t>
+          <t>¥992,699.32</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥-20,791.54</t>
+          <t>¥-7,300.68</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-2.08%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-25.48%</t>
+          <t>-9.26%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-2.841</v>
+        <v>-0.927</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3681,24 +3681,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.1209%</t>
+          <t>-0.0377%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>11.4230%</t>
+          <t>12.3666%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3825,26 +3825,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,008,890.44</t>
+          <t>¥1,010,094.44</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+8,890.44</t>
+          <t>¥+10,094.44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+13.19%</t>
+          <t>+14.25%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.869</v>
+        <v>2.08</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3853,24 +3853,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0528%</t>
+          <t>0.0565%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6.0600%</t>
+          <t>5.8942%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3901,26 +3901,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,006,861.48</t>
+          <t>¥1,008,315.28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+6,861.48</t>
+          <t>¥+8,315.28</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+10.05%</t>
+          <t>+11.61%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.55</v>
+        <v>1.868</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3929,24 +3929,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0408%</t>
+          <t>0.0466%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5.3576%</t>
+          <t>5.2202%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3977,26 +3977,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,007,817.21</t>
+          <t>¥1,009,244.51</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+7,817.21</t>
+          <t>¥+9,244.51</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+11.52%</t>
+          <t>+12.98%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.634</v>
+        <v>1.908</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -4005,24 +4005,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0465%</t>
+          <t>0.0518%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5.9626%</t>
+          <t>5.8050%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -4053,26 +4053,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,025,245.55</t>
+          <t>¥1,030,200.75</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+25,245.55</t>
+          <t>¥+30,200.75</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+2.52%</t>
+          <t>+3.02%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+41.77%</t>
+          <t>+48.38%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6.364</v>
+        <v>7.239</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -4081,24 +4081,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.1474%</t>
+          <t>0.1660%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5.5247%</t>
+          <t>5.5063%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -4129,26 +4129,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,029,043.50</t>
+          <t>¥1,030,515.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+29,043.50</t>
+          <t>¥+30,515.20</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.90%</t>
+          <t>+3.05%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+49.30%</t>
+          <t>+48.99%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3.657</v>
+        <v>3.727</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -4157,24 +4157,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.1710%</t>
+          <t>0.1695%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>11.2452%</t>
+          <t>10.9288%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
